--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:00</t>
+    <t xml:space="preserve">2026-09-09 22:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:51</t>
+    <t xml:space="preserve">2026-09-18 10:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:14</t>
+    <t xml:space="preserve">2026-09-23 12:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:18</t>
+    <t xml:space="preserve">2026-10-02 13:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Tirúa</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Hualqui</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Talcahuano</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:44</t>
+    <t xml:space="preserve">2026-10-04 08:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:37</t>
+    <t xml:space="preserve">2026-10-05 09:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
